--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487039_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487039_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8166</v>
+        <v>6.7823</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5701000000000001</v>
+        <v>1.7499</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2465</v>
+        <v>5.0323</v>
       </c>
       <c r="G2" t="n">
         <v>0.0595</v>
@@ -610,13 +610,13 @@
         <v>4.4392</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5433</v>
+        <v>0.4224</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.345</v>
+        <v>0.8349</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1983</v>
+        <v>-0.4125</v>
       </c>
       <c r="V2" t="n">
         <v>2.8263</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.755</v>
+        <v>5.9755</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4855</v>
+        <v>1.706</v>
       </c>
       <c r="F3" t="n">
         <v>4.2695</v>
@@ -688,10 +688,10 @@
         <v>4.8252</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.08989999999999999</v>
+        <v>1.1306</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.107</v>
+        <v>1.1135</v>
       </c>
       <c r="U3" t="n">
         <v>0.0172</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2026</v>
+        <v>4.0152</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3866</v>
+        <v>2.1456</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8161</v>
+        <v>1.8696</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7024</v>
@@ -766,13 +766,13 @@
         <v>3.0881</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1679</v>
+        <v>-0.0195</v>
       </c>
       <c r="T4" t="n">
-        <v>0.546</v>
+        <v>0.3051</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3781</v>
+        <v>-0.3246</v>
       </c>
       <c r="V4" t="n">
         <v>1.842</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6076</v>
+        <v>1.1289</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3123</v>
+        <v>0.8872</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2953</v>
+        <v>0.2418</v>
       </c>
       <c r="G5" t="n">
         <v>1.4835</v>
@@ -844,13 +844,13 @@
         <v>3.8602</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1325</v>
+        <v>1.6538</v>
       </c>
       <c r="T5" t="n">
-        <v>4.3877</v>
+        <v>1.9625</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2552</v>
+        <v>-0.3087</v>
       </c>
       <c r="V5" t="n">
         <v>-4.7105</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5088</v>
+        <v>0.0477</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.793</v>
+        <v>-3.0911</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3018</v>
+        <v>3.1388</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3045</v>
+        <v>0.104</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8454</v>
+        <v>-1.2897</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4591</v>
+        <v>1.3938</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.7972</v>
+        <v>-0.1629</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.211</v>
+        <v>-0.2279</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5073</v>
+        <v>0.267</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6344</v>
+        <v>-1.0618</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1271</v>
+        <v>1.3288</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9301</v>
+        <v>0.193</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-4.0532</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9301</v>
+        <v>4.2462</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5395</v>
+        <v>0.6927</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6604</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.121</v>
+        <v>-0.1464</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6562</v>
+        <v>-0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9931</v>
+        <v>0.0408</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6698</v>
+        <v>-1.2342</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6766</v>
+        <v>1.275</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8527</v>
+        <v>-2.3045</v>
       </c>
       <c r="H7" t="n">
-        <v>0.414</v>
+        <v>-1.8454</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2667</v>
+        <v>-0.4591</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2188</v>
+        <v>-1.7972</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3674</v>
+        <v>-1.211</v>
       </c>
       <c r="L7" t="n">
         <v>-0.5862000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6338</v>
+        <v>-0.5073</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0466</v>
+        <v>-0.6344</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6805</v>
+        <v>0.1271</v>
       </c>
       <c r="P7" t="n">
-        <v>0.579</v>
+        <v>1.9301</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5091</v>
+        <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4336</v>
+        <v>1.0715</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5208</v>
+        <v>1.2192</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0872</v>
+        <v>-0.1477</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2859</v>
+        <v>-0.6562</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SANCHEZ MARROYO</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0215</v>
+        <v>-0.3933</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8994</v>
+        <v>-1.9093</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1221</v>
+        <v>1.516</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7869</v>
+        <v>-0.8527</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5134</v>
+        <v>0.414</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2735</v>
+        <v>-1.2667</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6469</v>
+        <v>-0.2188</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6469</v>
+        <v>0.3674</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.14</v>
+        <v>-0.6338</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1335</v>
+        <v>0.0466</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2735</v>
+        <v>-0.6805</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.193</v>
+        <v>0.579</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.193</v>
+        <v>-1.9301</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0416</v>
+        <v>0.1662</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0595</v>
+        <v>0.2396</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0178</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1662</v>
+        <v>-0.7855</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5504</v>
+        <v>-1.25</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3842</v>
+        <v>0.4645</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2243</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0231</v>
+        <v>0.4039</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3702</v>
+        <v>0.6706</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.347</v>
+        <v>-0.2667</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>J. SANCHEZ MARROYO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4534</v>
+        <v>-0.9947</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5119</v>
+        <v>-0.8994</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0584</v>
+        <v>-0.0953</v>
       </c>
       <c r="G10" t="n">
-        <v>0.104</v>
+        <v>-0.7869</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2897</v>
+        <v>-0.5134</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3938</v>
+        <v>-0.2735</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1629</v>
+        <v>-0.6469</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2279</v>
+        <v>-0.6469</v>
       </c>
       <c r="L10" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.267</v>
+        <v>-0.14</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0618</v>
+        <v>0.1335</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3288</v>
+        <v>-0.2735</v>
       </c>
       <c r="P10" t="n">
-        <v>0.193</v>
+        <v>-0.193</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.0532</v>
+        <v>-0.193</v>
       </c>
       <c r="R10" t="n">
-        <v>4.2462</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8084</v>
+        <v>-0.0149</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5816</v>
+        <v>-0.0595</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2267</v>
+        <v>0.0446</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2216</v>
+        <v>-4.8899</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2489</v>
+        <v>-4.1313</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9727</v>
+        <v>-0.7585</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0521</v>
@@ -1312,13 +1312,13 @@
         <v>3.0881</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1284</v>
+        <v>1.4601</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7868</v>
+        <v>1.9043</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6584</v>
+        <v>-0.4442</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4559</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.0348</v>
+        <v>10.927</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.918899999999999</v>
+        <v>-6.026600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>16.9536</v>
+        <v>16.9537</v>
       </c>
       <c r="G12" t="n">
         <v>-6.110200000000001</v>
@@ -1369,13 +1369,13 @@
         <v>0.9713999999999996</v>
       </c>
       <c r="L12" t="n">
-        <v>-6.515199999999999</v>
+        <v>-6.5152</v>
       </c>
       <c r="M12" t="n">
         <v>-0.5661999999999998</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.8106</v>
+        <v>-5.810600000000001</v>
       </c>
       <c r="O12" t="n">
         <v>5.244299999999999</v>
@@ -1390,13 +1390,13 @@
         <v>28.9512</v>
       </c>
       <c r="S12" t="n">
-        <v>6.074600000000001</v>
+        <v>6.966799999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>8.1372</v>
+        <v>9.029399999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.0625</v>
+        <v>-2.0624</v>
       </c>
       <c r="V12" t="n">
         <v>-3.4402</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. FRECHILLA GOMEZ</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9841</v>
+        <v>4.1291</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8773</v>
+        <v>1.4206</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1068</v>
+        <v>2.7085</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1989</v>
+        <v>3.6095</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4046</v>
+        <v>1.3725</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7943</v>
+        <v>2.237</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6778</v>
+        <v>2.0009</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0595</v>
+        <v>1.3661</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.6348</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5211</v>
+        <v>1.6086</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6549</v>
+        <v>0.0064</v>
       </c>
       <c r="O13" t="n">
-        <v>1.176</v>
+        <v>1.6022</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0.386</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0881</v>
+        <v>-0.965</v>
       </c>
       <c r="R13" t="n">
-        <v>3.0881</v>
+        <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7852</v>
+        <v>-0.3999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0597</v>
+        <v>0.3847</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.2744</v>
+        <v>-0.7846</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5334</v>
       </c>
       <c r="W13" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.228</v>
+        <v>0.5334</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>A. FRECHILLA GOMEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4873</v>
+        <v>3.0224</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4206</v>
+        <v>1.6756</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0667</v>
+        <v>1.3468</v>
       </c>
       <c r="G14" t="n">
-        <v>3.6095</v>
+        <v>3.1989</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3725</v>
+        <v>1.4046</v>
       </c>
       <c r="I14" t="n">
-        <v>2.237</v>
+        <v>1.7943</v>
       </c>
       <c r="J14" t="n">
-        <v>2.0009</v>
+        <v>2.6778</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3661</v>
+        <v>2.0595</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6348</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6086</v>
+        <v>0.5211</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0064</v>
+        <v>-0.6549</v>
       </c>
       <c r="O14" t="n">
-        <v>1.6022</v>
+        <v>1.176</v>
       </c>
       <c r="P14" t="n">
-        <v>0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>-3.0881</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3511</v>
+        <v>3.0881</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0417</v>
+        <v>-0.1765</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3847</v>
+        <v>0.858</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.4264</v>
+        <v>-1.0345</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5334</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X14" t="n">
-        <v>0.5334</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1753</v>
+        <v>1.3557</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0369</v>
+        <v>0.0633</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2122</v>
+        <v>1.2925</v>
       </c>
       <c r="G15" t="n">
         <v>0.8098</v>
@@ -1624,13 +1624,13 @@
         <v>0.772</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4065</v>
+        <v>-0.2261</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.119</v>
+        <v>-0.0188</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2875</v>
+        <v>-0.2072</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1623</v>
+        <v>0.2155</v>
       </c>
       <c r="E16" t="n">
         <v>-0.0595</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2218</v>
+        <v>0.275</v>
       </c>
       <c r="G16" t="n">
         <v>0.4606</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1104</v>
+        <v>0.1636</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1699</v>
+        <v>0.2231</v>
       </c>
       <c r="V16" t="n">
         <v>-0.4087</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0593</v>
+        <v>-1.3401</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.3688</v>
+        <v>-3.5677</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3096</v>
+        <v>2.2276</v>
       </c>
       <c r="G17" t="n">
         <v>-2.1881</v>
@@ -1780,13 +1780,13 @@
         <v>2.7021</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9836</v>
+        <v>-0.2644</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7297</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2539</v>
+        <v>-0.3358</v>
       </c>
       <c r="V17" t="n">
         <v>0.5334</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5634</v>
+        <v>-1.6164</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.1787</v>
+        <v>-1.4697</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6153</v>
+        <v>-0.1467</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4356</v>
+        <v>1.7297</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0588</v>
+        <v>2.7293</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4944</v>
+        <v>-0.9996</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0157</v>
+        <v>1.6022</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3195</v>
+        <v>2.9702</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3352</v>
+        <v>-1.368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4199</v>
+        <v>0.1275</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2607</v>
+        <v>-0.2409</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1592</v>
+        <v>0.3684</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.8602</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.0182</v>
+        <v>-4.0532</v>
       </c>
       <c r="R18" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0132</v>
+        <v>-1.0457</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0132</v>
+        <v>0.1236</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>-1.1693</v>
       </c>
       <c r="V18" t="n">
-        <v>1.7192</v>
+        <v>-0.3704</v>
       </c>
       <c r="W18" t="n">
-        <v>1.842</v>
+        <v>0.8576</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1228</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9397</v>
+        <v>-2.2567</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.67</v>
+        <v>-3.379</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2697</v>
+        <v>1.1223</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7297</v>
+        <v>-0.4356</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7293</v>
+        <v>1.0588</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9996</v>
+        <v>-1.4944</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6022</v>
+        <v>-0.0157</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9702</v>
+        <v>1.3195</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.368</v>
+        <v>-1.3352</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1275</v>
+        <v>-0.4199</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2409</v>
+        <v>-0.2607</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3684</v>
+        <v>-0.1592</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.9301</v>
+        <v>-3.8602</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.0532</v>
+        <v>-5.0182</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.369</v>
+        <v>0.3199</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0766</v>
+        <v>-0.187</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.2923</v>
+        <v>0.507</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3704</v>
+        <v>1.7192</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8576</v>
+        <v>1.842</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.228</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.1264</v>
+        <v>-4.2047</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.1397</v>
+        <v>-5.9395</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0133</v>
+        <v>1.7348</v>
       </c>
       <c r="G20" t="n">
         <v>1.0026</v>
@@ -2014,13 +2014,13 @@
         <v>2.7021</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3438</v>
+        <v>-0.4221</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0026</v>
+        <v>0.1977</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3412</v>
+        <v>-0.6197</v>
       </c>
       <c r="V20" t="n">
         <v>1.391</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.1549</v>
+        <v>-6.0015</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.4119</v>
+        <v>-6.3118</v>
       </c>
       <c r="F21" t="n">
-        <v>0.257</v>
+        <v>0.3102</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0772</v>
@@ -2092,13 +2092,13 @@
         <v>1.5441</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8388</v>
+        <v>-0.6855</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5923</v>
+        <v>0.6924</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4311</v>
+        <v>-1.3779</v>
       </c>
       <c r="V21" t="n">
         <v>0.0422</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-10.0347</v>
+        <v>-6.6967</v>
       </c>
       <c r="E22" t="n">
-        <v>-17.5676</v>
+        <v>-17.5677</v>
       </c>
       <c r="F22" t="n">
-        <v>7.532999999999999</v>
+        <v>10.871</v>
       </c>
       <c r="G22" t="n">
         <v>6.110200000000001</v>
@@ -2149,13 +2149,13 @@
         <v>5.8106</v>
       </c>
       <c r="L22" t="n">
-        <v>-5.2442</v>
+        <v>-5.244199999999999</v>
       </c>
       <c r="M22" t="n">
         <v>5.5439</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9714000000000002</v>
+        <v>-0.9714</v>
       </c>
       <c r="O22" t="n">
         <v>6.5154</v>
@@ -2170,19 +2170,19 @@
         <v>15.4406</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.0746</v>
+        <v>-2.7367</v>
       </c>
       <c r="T22" t="n">
         <v>2.0625</v>
       </c>
       <c r="U22" t="n">
-        <v>-8.136900000000001</v>
+        <v>-4.7989</v>
       </c>
       <c r="V22" t="n">
-        <v>3.4401</v>
+        <v>3.440099999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>8.755000000000001</v>
+        <v>8.754999999999999</v>
       </c>
       <c r="X22" t="n">
         <v>-5.3147</v>
